--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513661_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513661_FASEFINALBFFB3_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1952</v>
+        <v>1.5887</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3431</v>
+        <v>0.8479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8521</v>
+        <v>0.7408</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2913</v>
@@ -610,13 +610,13 @@
         <v>0.7789</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7075</v>
+        <v>1.1011</v>
       </c>
       <c r="T2" t="n">
-        <v>2.191</v>
+        <v>0.6959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5165</v>
+        <v>0.4052</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8471</v>
+        <v>1.1626</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5998</v>
+        <v>2.3866</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7527</v>
+        <v>-1.224</v>
       </c>
       <c r="G3" t="n">
         <v>1.6534</v>
@@ -688,13 +688,13 @@
         <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3029</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2695</v>
+        <v>-0.4827</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.349</v>
+        <v>0.1797</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3826</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5698</v>
+        <v>0.8712</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7847</v>
+        <v>1.1696</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2149</v>
+        <v>-0.2984</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3356</v>
@@ -766,13 +766,13 @@
         <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3215</v>
+        <v>-0.0201</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8011</v>
+        <v>-0.4162</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4796</v>
+        <v>0.3961</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3311</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4824</v>
+        <v>0.2815</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5786</v>
+        <v>-0.2471</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4755</v>
+        <v>0.5555</v>
       </c>
       <c r="H5" t="n">
-        <v>1.384</v>
+        <v>0.4613</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8595</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8691</v>
+        <v>0.2963</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3471</v>
+        <v>0.3284</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.478</v>
+        <v>-0.0322</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3446</v>
+        <v>0.2592</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0369</v>
+        <v>0.1329</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3815</v>
+        <v>0.1263</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0091</v>
+        <v>0.0378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3867</v>
+        <v>-0.0148</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3775</v>
+        <v>0.0526</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1695</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1695</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1766</v>
+        <v>-0.1763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1818</v>
+        <v>0.0464</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3584</v>
+        <v>-0.2227</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5555</v>
+        <v>0.4681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4613</v>
+        <v>-0.216</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.6842</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2963</v>
+        <v>0.0944</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3284</v>
+        <v>0.0616</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0322</v>
+        <v>0.0328</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2592</v>
+        <v>0.3738</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1329</v>
+        <v>-0.2776</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1263</v>
+        <v>0.6514</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1731</v>
+        <v>-0.0076</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1144</v>
+        <v>-0.048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0587</v>
+        <v>0.0404</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.2211</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.3605</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3385</v>
+        <v>0.4686</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3062</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4681</v>
+        <v>-0.4755</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.216</v>
+        <v>1.384</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6842</v>
+        <v>-1.8595</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0944</v>
+        <v>0.8691</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0616</v>
+        <v>1.3471</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0328</v>
+        <v>-0.478</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3738</v>
+        <v>-1.3446</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2776</v>
+        <v>0.0369</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6514</v>
+        <v>-1.3815</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.476</v>
+        <v>-0.2734</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4328</v>
+        <v>-0.4005</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0431</v>
+        <v>0.1271</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2211</v>
+        <v>-1.1695</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2211</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5041</v>
+        <v>-1.5271</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8428</v>
+        <v>-1.1133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6613</v>
+        <v>-0.4138</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4452</v>
+        <v>-1.8663</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1484</v>
+        <v>0.7661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7032</v>
+        <v>-2.6324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.8125</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5695</v>
+        <v>0.4516</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2808</v>
+        <v>-1.264</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1564</v>
+        <v>-1.0539</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5789</v>
+        <v>0.3145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5775</v>
+        <v>-1.3684</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1421</v>
+        <v>0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0863</v>
+        <v>-0.6345</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0235</v>
+        <v>-0.3009</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9372</v>
+        <v>-0.3336</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1695</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1044</v>
+        <v>-1.8011</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4124</v>
+        <v>-0.4441</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6921</v>
+        <v>-1.357</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8663</v>
+        <v>-0.4452</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7661</v>
+        <v>-1.1484</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6324</v>
+        <v>0.7032</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8125</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4516</v>
+        <v>-0.5695</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.264</v>
+        <v>1.2808</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0539</v>
+        <v>-1.1564</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3145</v>
+        <v>-0.5789</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3684</v>
+        <v>-0.5775</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9737</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2118</v>
+        <v>-0.3832</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5999</v>
+        <v>-0.6248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6119</v>
+        <v>0.2416</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.1695</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3905</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0153</v>
+        <v>-2.2085</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0705</v>
+        <v>-1.4863</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9447</v>
+        <v>-0.7221</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5979</v>
@@ -1234,13 +1234,13 @@
         <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5595</v>
+        <v>0.2473</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6802</v>
+        <v>-0.096</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1207</v>
+        <v>0.3433</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4421</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5405</v>
+        <v>-4.1256</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3469</v>
+        <v>-3.8485</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1936</v>
+        <v>-0.2771</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5799</v>
@@ -1312,13 +1312,13 @@
         <v>1.7526</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8438</v>
+        <v>-0.4289</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0853</v>
+        <v>-0.587</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2415</v>
+        <v>0.158</v>
       </c>
       <c r="V11" t="n">
         <v>0.0516</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.4697</v>
+        <v>-6.542199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6193</v>
+        <v>-1.6916</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8504</v>
+        <v>-4.8505</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9147</v>
       </c>
       <c r="H12" t="n">
-        <v>7.546099999999999</v>
+        <v>7.546100000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-11.4606</v>
@@ -1366,7 +1366,7 @@
         <v>7.1104</v>
       </c>
       <c r="K12" t="n">
-        <v>8.8089</v>
+        <v>8.808900000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-1.6983</v>
@@ -1390,13 +1390,13 @@
         <v>11.6841</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.592</v>
+        <v>-0.6643999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.202400000000001</v>
+        <v>-2.275</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6103</v>
+        <v>1.6104</v>
       </c>
       <c r="V12" t="n">
         <v>-4.884300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9301</v>
+        <v>5.4293</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3575</v>
+        <v>2.5569</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5726</v>
+        <v>2.8724</v>
       </c>
       <c r="G13" t="n">
         <v>3.7472</v>
@@ -1468,13 +1468,13 @@
         <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.51</v>
+        <v>1.0092</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.2732</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4362</v>
+        <v>0.736</v>
       </c>
       <c r="V13" t="n">
         <v>0.4781</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7663</v>
+        <v>4.4447</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9703</v>
+        <v>3.5411</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.204</v>
+        <v>0.9036</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6452</v>
+        <v>3.1325</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4497</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0949</v>
+        <v>3.9275</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1516</v>
+        <v>3.852</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1437</v>
+        <v>1.0879</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0079</v>
+        <v>2.7642</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5064</v>
+        <v>-0.7195</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5934</v>
+        <v>-1.8828</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.1633</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1947</v>
+        <v>0.1947</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8962</v>
+        <v>-0.1036</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7661</v>
+        <v>-0.3636</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1301</v>
+        <v>0.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4197</v>
+        <v>1.2211</v>
       </c>
       <c r="W14" t="n">
         <v>1.2211</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9193</v>
+        <v>3.4133</v>
       </c>
       <c r="E15" t="n">
-        <v>2.943</v>
+        <v>3.0732</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0238</v>
+        <v>0.3401</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1325</v>
+        <v>1.6452</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-1.4497</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9275</v>
+        <v>3.0949</v>
       </c>
       <c r="J15" t="n">
-        <v>3.852</v>
+        <v>3.1516</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0879</v>
+        <v>0.1437</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7642</v>
+        <v>3.0079</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7195</v>
+        <v>-1.5064</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8828</v>
+        <v>-1.5934</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1633</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1947</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1684</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3632</v>
+        <v>0.9737</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.629</v>
+        <v>0.5431</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9617</v>
+        <v>-0.131</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6674</v>
+        <v>0.6742</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2211</v>
+        <v>1.4197</v>
       </c>
       <c r="W15" t="n">
         <v>1.2211</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0554</v>
+        <v>1.9935</v>
       </c>
       <c r="E16" t="n">
         <v>1.4635</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5919</v>
+        <v>0.53</v>
       </c>
       <c r="G16" t="n">
         <v>2.119</v>
@@ -1702,13 +1702,13 @@
         <v>1.1684</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6306</v>
+        <v>0.5687</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3064</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.8751</v>
       </c>
       <c r="V16" t="n">
         <v>0.2795</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2241</v>
+        <v>0.8284</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9182</v>
+        <v>2.1176</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6941</v>
+        <v>-1.2892</v>
       </c>
       <c r="G17" t="n">
         <v>-0.08210000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0309</v>
+        <v>0.5734</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0028</v>
+        <v>0.2021</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0337</v>
+        <v>0.3712</v>
       </c>
       <c r="V17" t="n">
         <v>2.8686</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3969</v>
+        <v>-0.772</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1844</v>
+        <v>-3.213</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7875</v>
+        <v>2.441</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1679</v>
+        <v>-2.0193</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9701</v>
+        <v>-0.4829</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8022</v>
+        <v>-1.5364</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.697</v>
+        <v>-2.0852</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9807</v>
+        <v>0.3618</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2837</v>
+        <v>-2.447</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4709</v>
+        <v>0.0659</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.8447</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5185</v>
+        <v>0.9106</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3632</v>
+        <v>-1.1684</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="S19" t="n">
-        <v>2.436</v>
+        <v>0.8539</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5962</v>
+        <v>0.0406</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8398</v>
+        <v>0.8133</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0808</v>
+        <v>0.1986</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3603</v>
+        <v>0.1986</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8314</v>
+        <v>-1.3789</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3127</v>
+        <v>-1.1142</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4813</v>
+        <v>-0.2647</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0193</v>
+        <v>-1.0507</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4829</v>
+        <v>-0.1478</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5364</v>
+        <v>-0.9029</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0852</v>
+        <v>0.0939</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3618</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.447</v>
+        <v>0.0733</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0659</v>
+        <v>-1.1446</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8447</v>
+        <v>-0.1684</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9106</v>
+        <v>-0.9762</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1684</v>
+        <v>-0.1947</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3632</v>
+        <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7945</v>
+        <v>-0.6329</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0591</v>
+        <v>-1.0134</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8536</v>
+        <v>0.3805</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1986</v>
+        <v>-0.2795</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1986</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8619</v>
+        <v>-1.836</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2139</v>
+        <v>-2.7825</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.648</v>
+        <v>0.9465</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0507</v>
+        <v>-2.1679</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1478</v>
+        <v>-2.9701</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9029</v>
+        <v>0.8022</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0939</v>
+        <v>-1.697</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0205</v>
+        <v>-1.9807</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0733</v>
+        <v>0.2837</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1446</v>
+        <v>-0.4709</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1684</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9762</v>
+        <v>0.5185</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1947</v>
+        <v>-1.3632</v>
       </c>
       <c r="R21" t="n">
         <v>0.7789</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1159</v>
+        <v>0.997</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.113</v>
+        <v>-0.0018</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0029</v>
+        <v>0.9988</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2795</v>
+        <v>-0.0808</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2795</v>
+        <v>-0.3603</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4681</v>
+        <v>-2.792</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.091</v>
+        <v>-0.792</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3771</v>
+        <v>-2</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5423</v>
@@ -2170,13 +2170,13 @@
         <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8995</v>
+        <v>-0.2233</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6091</v>
+        <v>-0.3101</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2904</v>
+        <v>0.0867</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2211</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.469800000000001</v>
+        <v>9.463199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>4.850500000000001</v>
+        <v>4.8506</v>
       </c>
       <c r="F23" t="n">
-        <v>2.619200000000001</v>
+        <v>4.6126</v>
       </c>
       <c r="G23" t="n">
-        <v>3.9145</v>
+        <v>3.914500000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-7.546</v>
@@ -2248,16 +2248,16 @@
         <v>8.7631</v>
       </c>
       <c r="S23" t="n">
-        <v>1.592</v>
+        <v>3.5855</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6103</v>
+        <v>-1.6104</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2023</v>
+        <v>5.1958</v>
       </c>
       <c r="V23" t="n">
-        <v>4.884200000000001</v>
+        <v>4.8842</v>
       </c>
       <c r="W23" t="n">
         <v>7.1202</v>
